--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117562343</v>
+        <v>117562328</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555158</v>
+        <v>555386</v>
       </c>
       <c r="R18" t="n">
-        <v>6977942</v>
+        <v>6978256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117562328</v>
+        <v>117562343</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555386</v>
+        <v>555158</v>
       </c>
       <c r="R19" t="n">
-        <v>6978256</v>
+        <v>6977942</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117562352</v>
+        <v>117562336</v>
       </c>
       <c r="B2" t="n">
-        <v>79596</v>
+        <v>79561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555286</v>
+        <v>555266</v>
       </c>
       <c r="R2" t="n">
-        <v>6977950</v>
+        <v>6978128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117562347</v>
+        <v>117562333</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555453</v>
+        <v>555290</v>
       </c>
       <c r="R4" t="n">
-        <v>6978167</v>
+        <v>6978061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117562324</v>
+        <v>117562316</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555448</v>
+        <v>555265</v>
       </c>
       <c r="R5" t="n">
-        <v>6977944</v>
+        <v>6978100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117562325</v>
+        <v>117562321</v>
       </c>
       <c r="B7" t="n">
         <v>79561</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555437</v>
+        <v>555285</v>
       </c>
       <c r="R7" t="n">
-        <v>6978005</v>
+        <v>6977952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562312</v>
+        <v>117562341</v>
       </c>
       <c r="B8" t="n">
-        <v>79562</v>
+        <v>79597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555319</v>
+        <v>555286</v>
       </c>
       <c r="R8" t="n">
-        <v>6978341</v>
+        <v>6977950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117562353</v>
+        <v>117562327</v>
       </c>
       <c r="B10" t="n">
-        <v>91164</v>
+        <v>79561</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555212</v>
+        <v>555454</v>
       </c>
       <c r="R10" t="n">
-        <v>6978071</v>
+        <v>6978263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117562351</v>
+        <v>117562343</v>
       </c>
       <c r="B11" t="n">
-        <v>91064</v>
+        <v>97836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555529</v>
+        <v>555158</v>
       </c>
       <c r="R11" t="n">
-        <v>6978135</v>
+        <v>6977942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117562348</v>
+        <v>117562326</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555296</v>
+        <v>555457</v>
       </c>
       <c r="R12" t="n">
-        <v>6978282</v>
+        <v>6978213</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117562313</v>
+        <v>117562322</v>
       </c>
       <c r="B13" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555159</v>
+        <v>555303</v>
       </c>
       <c r="R13" t="n">
-        <v>6978387</v>
+        <v>6977944</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117562316</v>
+        <v>117562323</v>
       </c>
       <c r="B14" t="n">
-        <v>79465</v>
+        <v>79561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555265</v>
+        <v>555358</v>
       </c>
       <c r="R14" t="n">
-        <v>6978100</v>
+        <v>6977917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117562338</v>
+        <v>117562345</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555243</v>
+        <v>555530</v>
       </c>
       <c r="R15" t="n">
-        <v>6978151</v>
+        <v>6978122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117562321</v>
+        <v>117562353</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>91164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555285</v>
+        <v>555212</v>
       </c>
       <c r="R16" t="n">
-        <v>6977952</v>
+        <v>6978071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117562322</v>
+        <v>117562351</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>91064</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555303</v>
+        <v>555529</v>
       </c>
       <c r="R17" t="n">
-        <v>6977944</v>
+        <v>6978135</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117562328</v>
+        <v>117562348</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555386</v>
+        <v>555296</v>
       </c>
       <c r="R18" t="n">
-        <v>6978256</v>
+        <v>6978282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117562343</v>
+        <v>117562330</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555158</v>
+        <v>555319</v>
       </c>
       <c r="R19" t="n">
-        <v>6977942</v>
+        <v>6978341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117562326</v>
+        <v>117562320</v>
       </c>
       <c r="B20" t="n">
         <v>79561</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555457</v>
+        <v>555230</v>
       </c>
       <c r="R20" t="n">
-        <v>6978213</v>
+        <v>6977971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117562346</v>
+        <v>117562319</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555470</v>
+        <v>555158</v>
       </c>
       <c r="R21" t="n">
-        <v>6978145</v>
+        <v>6977942</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117562323</v>
+        <v>117562306</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>95384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555358</v>
+        <v>555491</v>
       </c>
       <c r="R22" t="n">
-        <v>6977917</v>
+        <v>6978063</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117562344</v>
+        <v>117562342</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>79597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555447</v>
+        <v>555266</v>
       </c>
       <c r="R23" t="n">
-        <v>6978038</v>
+        <v>6978128</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117562333</v>
+        <v>117562328</v>
       </c>
       <c r="B24" t="n">
         <v>79561</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555290</v>
+        <v>555386</v>
       </c>
       <c r="R24" t="n">
-        <v>6978061</v>
+        <v>6978256</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117562320</v>
+        <v>117562331</v>
       </c>
       <c r="B25" t="n">
         <v>79561</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555230</v>
+        <v>555282</v>
       </c>
       <c r="R25" t="n">
-        <v>6977971</v>
+        <v>6978354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117562336</v>
+        <v>117562346</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555266</v>
+        <v>555470</v>
       </c>
       <c r="R26" t="n">
-        <v>6978128</v>
+        <v>6978145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117562330</v>
+        <v>117562352</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>79596</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555319</v>
+        <v>555286</v>
       </c>
       <c r="R27" t="n">
-        <v>6978341</v>
+        <v>6977950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117562331</v>
+        <v>117562338</v>
       </c>
       <c r="B28" t="n">
         <v>79561</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555282</v>
+        <v>555243</v>
       </c>
       <c r="R28" t="n">
-        <v>6978354</v>
+        <v>6978151</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117562342</v>
+        <v>117562312</v>
       </c>
       <c r="B29" t="n">
-        <v>79597</v>
+        <v>79562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555266</v>
+        <v>555319</v>
       </c>
       <c r="R29" t="n">
-        <v>6978128</v>
+        <v>6978341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117562345</v>
+        <v>117562344</v>
       </c>
       <c r="B30" t="n">
         <v>97836</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555530</v>
+        <v>555447</v>
       </c>
       <c r="R30" t="n">
-        <v>6978122</v>
+        <v>6978038</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117562341</v>
+        <v>117562350</v>
       </c>
       <c r="B31" t="n">
-        <v>79597</v>
+        <v>90517</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555286</v>
+        <v>555469</v>
       </c>
       <c r="R31" t="n">
-        <v>6977950</v>
+        <v>6978058</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117562350</v>
+        <v>117562325</v>
       </c>
       <c r="B32" t="n">
-        <v>90517</v>
+        <v>79561</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555469</v>
+        <v>555437</v>
       </c>
       <c r="R32" t="n">
-        <v>6978058</v>
+        <v>6978005</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117562327</v>
+        <v>117562324</v>
       </c>
       <c r="B33" t="n">
         <v>79561</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555454</v>
+        <v>555448</v>
       </c>
       <c r="R33" t="n">
-        <v>6978263</v>
+        <v>6977944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117562319</v>
+        <v>117562347</v>
       </c>
       <c r="B34" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3951,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555158</v>
+        <v>555453</v>
       </c>
       <c r="R34" t="n">
-        <v>6977942</v>
+        <v>6978167</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117562306</v>
+        <v>117562313</v>
       </c>
       <c r="B35" t="n">
-        <v>95384</v>
+        <v>79562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555491</v>
+        <v>555159</v>
       </c>
       <c r="R35" t="n">
-        <v>6978063</v>
+        <v>6978387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117562336</v>
+        <v>117562333</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555266</v>
+        <v>555290</v>
       </c>
       <c r="R2" t="n">
-        <v>6978128</v>
+        <v>6978061</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117562311</v>
+        <v>117562331</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>79563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555457</v>
+        <v>555282</v>
       </c>
       <c r="R3" t="n">
-        <v>6978213</v>
+        <v>6978354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117562333</v>
+        <v>117562341</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>79599</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555290</v>
+        <v>555286</v>
       </c>
       <c r="R4" t="n">
-        <v>6978061</v>
+        <v>6977950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117562316</v>
+        <v>117562336</v>
       </c>
       <c r="B5" t="n">
-        <v>79465</v>
+        <v>79563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555265</v>
+        <v>555266</v>
       </c>
       <c r="R5" t="n">
-        <v>6978100</v>
+        <v>6978128</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117562315</v>
+        <v>117562328</v>
       </c>
       <c r="B6" t="n">
-        <v>79465</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555221</v>
+        <v>555386</v>
       </c>
       <c r="R6" t="n">
-        <v>6978402</v>
+        <v>6978256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>117562321</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562341</v>
+        <v>117562347</v>
       </c>
       <c r="B8" t="n">
-        <v>79597</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555286</v>
+        <v>555453</v>
       </c>
       <c r="R8" t="n">
-        <v>6977950</v>
+        <v>6978167</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117562332</v>
+        <v>117562344</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555143</v>
+        <v>555447</v>
       </c>
       <c r="R9" t="n">
-        <v>6978375</v>
+        <v>6978038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117562327</v>
+        <v>117562332</v>
       </c>
       <c r="B10" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555454</v>
+        <v>555143</v>
       </c>
       <c r="R10" t="n">
-        <v>6978263</v>
+        <v>6978375</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117562343</v>
+        <v>117562313</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>79564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555158</v>
+        <v>555159</v>
       </c>
       <c r="R11" t="n">
-        <v>6977942</v>
+        <v>6978387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>117562326</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117562322</v>
+        <v>117562325</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555303</v>
+        <v>555437</v>
       </c>
       <c r="R13" t="n">
-        <v>6977944</v>
+        <v>6978005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117562323</v>
+        <v>117562306</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>95386</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555358</v>
+        <v>555491</v>
       </c>
       <c r="R14" t="n">
-        <v>6977917</v>
+        <v>6978063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117562345</v>
+        <v>117562352</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>79598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555530</v>
+        <v>555286</v>
       </c>
       <c r="R15" t="n">
-        <v>6978122</v>
+        <v>6977950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117562353</v>
+        <v>117562315</v>
       </c>
       <c r="B16" t="n">
-        <v>91164</v>
+        <v>79467</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555212</v>
+        <v>555221</v>
       </c>
       <c r="R16" t="n">
-        <v>6978071</v>
+        <v>6978402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117562351</v>
+        <v>117562316</v>
       </c>
       <c r="B17" t="n">
-        <v>91064</v>
+        <v>79467</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555529</v>
+        <v>555265</v>
       </c>
       <c r="R17" t="n">
-        <v>6978135</v>
+        <v>6978100</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117562348</v>
+        <v>117562322</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555296</v>
+        <v>555303</v>
       </c>
       <c r="R18" t="n">
-        <v>6978282</v>
+        <v>6977944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117562330</v>
+        <v>117562338</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555319</v>
+        <v>555243</v>
       </c>
       <c r="R19" t="n">
-        <v>6978341</v>
+        <v>6978151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117562320</v>
+        <v>117562345</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555230</v>
+        <v>555530</v>
       </c>
       <c r="R20" t="n">
-        <v>6977971</v>
+        <v>6978122</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117562319</v>
+        <v>117562350</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>90519</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555158</v>
+        <v>555469</v>
       </c>
       <c r="R21" t="n">
-        <v>6977942</v>
+        <v>6978058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117562306</v>
+        <v>117562327</v>
       </c>
       <c r="B22" t="n">
-        <v>95384</v>
+        <v>79563</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555491</v>
+        <v>555454</v>
       </c>
       <c r="R22" t="n">
-        <v>6978063</v>
+        <v>6978263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117562342</v>
+        <v>117562312</v>
       </c>
       <c r="B23" t="n">
-        <v>79597</v>
+        <v>79564</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555266</v>
+        <v>555319</v>
       </c>
       <c r="R23" t="n">
-        <v>6978128</v>
+        <v>6978341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117562328</v>
+        <v>117562319</v>
       </c>
       <c r="B24" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555386</v>
+        <v>555158</v>
       </c>
       <c r="R24" t="n">
-        <v>6978256</v>
+        <v>6977942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117562331</v>
+        <v>117562346</v>
       </c>
       <c r="B25" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555282</v>
+        <v>555470</v>
       </c>
       <c r="R25" t="n">
-        <v>6978354</v>
+        <v>6978145</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117562346</v>
+        <v>117562348</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555470</v>
+        <v>555296</v>
       </c>
       <c r="R26" t="n">
-        <v>6978145</v>
+        <v>6978282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117562352</v>
+        <v>117562311</v>
       </c>
       <c r="B27" t="n">
-        <v>79596</v>
+        <v>79592</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555286</v>
+        <v>555457</v>
       </c>
       <c r="R27" t="n">
-        <v>6977950</v>
+        <v>6978213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117562338</v>
+        <v>117562343</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555243</v>
+        <v>555158</v>
       </c>
       <c r="R28" t="n">
-        <v>6978151</v>
+        <v>6977942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117562312</v>
+        <v>117562351</v>
       </c>
       <c r="B29" t="n">
-        <v>79562</v>
+        <v>91066</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555319</v>
+        <v>555529</v>
       </c>
       <c r="R29" t="n">
-        <v>6978341</v>
+        <v>6978135</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117562344</v>
+        <v>117562342</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>79599</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3543,25 +3543,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555447</v>
+        <v>555266</v>
       </c>
       <c r="R30" t="n">
-        <v>6978038</v>
+        <v>6978128</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117562350</v>
+        <v>117562330</v>
       </c>
       <c r="B31" t="n">
-        <v>90517</v>
+        <v>79563</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555469</v>
+        <v>555319</v>
       </c>
       <c r="R31" t="n">
-        <v>6978058</v>
+        <v>6978341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117562325</v>
+        <v>117562323</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555437</v>
+        <v>555358</v>
       </c>
       <c r="R32" t="n">
-        <v>6978005</v>
+        <v>6977917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
         <v>117562324</v>
       </c>
       <c r="B33" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117562347</v>
+        <v>117562320</v>
       </c>
       <c r="B34" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3951,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555453</v>
+        <v>555230</v>
       </c>
       <c r="R34" t="n">
-        <v>6978167</v>
+        <v>6977971</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117562313</v>
+        <v>117562353</v>
       </c>
       <c r="B35" t="n">
-        <v>79562</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555159</v>
+        <v>555212</v>
       </c>
       <c r="R35" t="n">
-        <v>6978387</v>
+        <v>6978071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117562321</v>
+        <v>117562347</v>
       </c>
       <c r="B7" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555285</v>
+        <v>555453</v>
       </c>
       <c r="R7" t="n">
-        <v>6977952</v>
+        <v>6978167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562347</v>
+        <v>117562321</v>
       </c>
       <c r="B8" t="n">
-        <v>97838</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555453</v>
+        <v>555285</v>
       </c>
       <c r="R8" t="n">
-        <v>6978167</v>
+        <v>6977952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117562344</v>
+        <v>117562313</v>
       </c>
       <c r="B9" t="n">
-        <v>97838</v>
+        <v>79564</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555447</v>
+        <v>555159</v>
       </c>
       <c r="R9" t="n">
-        <v>6978038</v>
+        <v>6978387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117562332</v>
+        <v>117562344</v>
       </c>
       <c r="B10" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555143</v>
+        <v>555447</v>
       </c>
       <c r="R10" t="n">
-        <v>6978375</v>
+        <v>6978038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117562313</v>
+        <v>117562332</v>
       </c>
       <c r="B11" t="n">
-        <v>79564</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555159</v>
+        <v>555143</v>
       </c>
       <c r="R11" t="n">
-        <v>6978387</v>
+        <v>6978375</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117562311</v>
+        <v>117562343</v>
       </c>
       <c r="B27" t="n">
-        <v>79592</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555457</v>
+        <v>555158</v>
       </c>
       <c r="R27" t="n">
-        <v>6978213</v>
+        <v>6977942</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117562343</v>
+        <v>117562311</v>
       </c>
       <c r="B28" t="n">
-        <v>97838</v>
+        <v>79592</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3339,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555158</v>
+        <v>555457</v>
       </c>
       <c r="R28" t="n">
-        <v>6977942</v>
+        <v>6978213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117562325</v>
+        <v>117562306</v>
       </c>
       <c r="B2" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555437</v>
+        <v>555491</v>
       </c>
       <c r="R2" t="n">
-        <v>6978005</v>
+        <v>6978063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117562350</v>
+        <v>117562351</v>
       </c>
       <c r="B3" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555469</v>
+        <v>555529</v>
       </c>
       <c r="R3" t="n">
-        <v>6978058</v>
+        <v>6978135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117562341</v>
+        <v>117562353</v>
       </c>
       <c r="B4" t="n">
-        <v>79599</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555286</v>
+        <v>555212</v>
       </c>
       <c r="R4" t="n">
-        <v>6977950</v>
+        <v>6978071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117562338</v>
+        <v>117562312</v>
       </c>
       <c r="B5" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555243</v>
+        <v>555319</v>
       </c>
       <c r="R5" t="n">
-        <v>6978151</v>
+        <v>6978341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117562311</v>
+        <v>117562313</v>
       </c>
       <c r="B6" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555457</v>
+        <v>555159</v>
       </c>
       <c r="R6" t="n">
-        <v>6978213</v>
+        <v>6978387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117562353</v>
+        <v>117562315</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555212</v>
+        <v>555221</v>
       </c>
       <c r="R7" t="n">
-        <v>6978071</v>
+        <v>6978402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117562327</v>
+        <v>117562316</v>
       </c>
       <c r="B8" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555454</v>
+        <v>555265</v>
       </c>
       <c r="R8" t="n">
-        <v>6978263</v>
+        <v>6978100</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117562313</v>
+        <v>117562319</v>
       </c>
       <c r="B9" t="n">
-        <v>79564</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555159</v>
+        <v>555158</v>
       </c>
       <c r="R9" t="n">
-        <v>6978387</v>
+        <v>6977942</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117562319</v>
+        <v>117562320</v>
       </c>
       <c r="B10" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555158</v>
+        <v>555230</v>
       </c>
       <c r="R10" t="n">
-        <v>6977942</v>
+        <v>6977971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117562328</v>
+        <v>117562321</v>
       </c>
       <c r="B11" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555386</v>
+        <v>555285</v>
       </c>
       <c r="R11" t="n">
-        <v>6978256</v>
+        <v>6977952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117562306</v>
+        <v>117562322</v>
       </c>
       <c r="B12" t="n">
-        <v>95386</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555491</v>
+        <v>555303</v>
       </c>
       <c r="R12" t="n">
-        <v>6978063</v>
+        <v>6977944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117562348</v>
+        <v>117562323</v>
       </c>
       <c r="B13" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555296</v>
+        <v>555358</v>
       </c>
       <c r="R13" t="n">
-        <v>6978282</v>
+        <v>6977917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117562322</v>
+        <v>117562324</v>
       </c>
       <c r="B14" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1874,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555303</v>
+        <v>555448</v>
       </c>
       <c r="R14" t="n">
         <v>6977944</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117562323</v>
+        <v>117562325</v>
       </c>
       <c r="B15" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555358</v>
+        <v>555437</v>
       </c>
       <c r="R15" t="n">
-        <v>6977917</v>
+        <v>6978005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117562330</v>
+        <v>117562326</v>
       </c>
       <c r="B16" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555319</v>
+        <v>555457</v>
       </c>
       <c r="R16" t="n">
-        <v>6978341</v>
+        <v>6978213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117562351</v>
+        <v>117562327</v>
       </c>
       <c r="B17" t="n">
-        <v>91066</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555529</v>
+        <v>555454</v>
       </c>
       <c r="R17" t="n">
-        <v>6978135</v>
+        <v>6978263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117562345</v>
+        <v>117562328</v>
       </c>
       <c r="B18" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555530</v>
+        <v>555386</v>
       </c>
       <c r="R18" t="n">
-        <v>6978122</v>
+        <v>6978256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117562343</v>
+        <v>117562330</v>
       </c>
       <c r="B19" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555158</v>
+        <v>555319</v>
       </c>
       <c r="R19" t="n">
-        <v>6977942</v>
+        <v>6978341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,12 +2424,7 @@
         <v>117562331</v>
       </c>
       <c r="B20" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117562342</v>
+        <v>117562332</v>
       </c>
       <c r="B21" t="n">
-        <v>79599</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555266</v>
+        <v>555143</v>
       </c>
       <c r="R21" t="n">
-        <v>6978128</v>
+        <v>6978375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117562344</v>
+        <v>117562333</v>
       </c>
       <c r="B22" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555447</v>
+        <v>555290</v>
       </c>
       <c r="R22" t="n">
-        <v>6978038</v>
+        <v>6978061</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117562316</v>
+        <v>117562336</v>
       </c>
       <c r="B23" t="n">
-        <v>79467</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555265</v>
+        <v>555266</v>
       </c>
       <c r="R23" t="n">
-        <v>6978100</v>
+        <v>6978128</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117562321</v>
+        <v>117562338</v>
       </c>
       <c r="B24" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555285</v>
+        <v>555243</v>
       </c>
       <c r="R24" t="n">
-        <v>6977952</v>
+        <v>6978151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117562336</v>
+        <v>117562311</v>
       </c>
       <c r="B25" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555266</v>
+        <v>555457</v>
       </c>
       <c r="R25" t="n">
-        <v>6978128</v>
+        <v>6978213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117562324</v>
+        <v>117562352</v>
       </c>
       <c r="B26" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555448</v>
+        <v>555286</v>
       </c>
       <c r="R26" t="n">
-        <v>6977944</v>
+        <v>6977950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117562352</v>
+        <v>117562341</v>
       </c>
       <c r="B27" t="n">
-        <v>79598</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3327,37 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117562326</v>
+        <v>117562342</v>
       </c>
       <c r="B28" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555457</v>
+        <v>555266</v>
       </c>
       <c r="R28" t="n">
-        <v>6978213</v>
+        <v>6978128</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,37 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117562332</v>
+        <v>117562343</v>
       </c>
       <c r="B29" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555143</v>
+        <v>555158</v>
       </c>
       <c r="R29" t="n">
-        <v>6978375</v>
+        <v>6977942</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117562347</v>
+        <v>117562344</v>
       </c>
       <c r="B30" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555453</v>
+        <v>555447</v>
       </c>
       <c r="R30" t="n">
-        <v>6978167</v>
+        <v>6978038</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117562333</v>
+        <v>117562345</v>
       </c>
       <c r="B31" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555290</v>
+        <v>555530</v>
       </c>
       <c r="R31" t="n">
-        <v>6978061</v>
+        <v>6978122</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,37 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117562315</v>
+        <v>117562346</v>
       </c>
       <c r="B32" t="n">
-        <v>79467</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555221</v>
+        <v>555470</v>
       </c>
       <c r="R32" t="n">
-        <v>6978402</v>
+        <v>6978145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117562312</v>
+        <v>117562347</v>
       </c>
       <c r="B33" t="n">
-        <v>79564</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555319</v>
+        <v>555453</v>
       </c>
       <c r="R33" t="n">
-        <v>6978341</v>
+        <v>6978167</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,37 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117562320</v>
+        <v>117562348</v>
       </c>
       <c r="B34" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555230</v>
+        <v>555296</v>
       </c>
       <c r="R34" t="n">
-        <v>6977971</v>
+        <v>6978282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,108 +3873,6 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>117562346</v>
-      </c>
-      <c r="B35" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Vallsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>555470</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6978145</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58080-2023 artfynd.xlsx
+++ b/artfynd/A 58080-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562306</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562351</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562316</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562320</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562323</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562324</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562326</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562328</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562333</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562336</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562338</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562311</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562352</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562341</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562342</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562343</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562344</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562345</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562346</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562347</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562348</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562312</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562313</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562315</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562330</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562331</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,8 +4038,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>